--- a/src/assets/excel/template-thr.xlsx
+++ b/src/assets/excel/template-thr.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\gbvh\src\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2B904F-1338-4EE5-9F4F-D476F24A0E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2161CC-77A2-4F6B-98F9-9F0E83CF74F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="2730" windowWidth="18780" windowHeight="9840" xr2:uid="{D20C10B8-C708-4404-8118-FB0D135168E9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D20C10B8-C708-4404-8118-FB0D135168E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,63 +25,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>NIK</t>
-  </si>
-  <si>
-    <t>TANGGAL_MASUK</t>
-  </si>
-  <si>
-    <t>TANGGAL_KELUAR</t>
-  </si>
-  <si>
-    <t>GAJI_POKOK</t>
-  </si>
-  <si>
-    <t>TUNJANGAN_MASA_KERJA</t>
-  </si>
-  <si>
-    <t>TUNJANGAN_JABATAN</t>
-  </si>
-  <si>
-    <t>TUNJANGAN_TIDAK_TETAP</t>
-  </si>
-  <si>
-    <t>YEAR</t>
-  </si>
-  <si>
-    <t>DEPARTEMEN</t>
-  </si>
-  <si>
-    <t>BAGIAN</t>
-  </si>
-  <si>
-    <t>JABATAN</t>
-  </si>
-  <si>
-    <t>GRADE</t>
-  </si>
-  <si>
-    <t>NAMA_KARYAWAN</t>
-  </si>
-  <si>
-    <t>STATUS_PAJAK</t>
-  </si>
-  <si>
-    <t>MASA_KERJA</t>
-  </si>
-  <si>
-    <t>TOTAL_UPAH</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>THR_BRUTO</t>
   </si>
   <si>
-    <t>PPH_21</t>
-  </si>
-  <si>
     <t>THR_BERSIH</t>
+  </si>
+  <si>
+    <t>HARTANTI</t>
+  </si>
+  <si>
+    <t>SRI WAHYUNINGSIH</t>
+  </si>
+  <si>
+    <t>TK/0</t>
+  </si>
+  <si>
+    <t>THR_YEAR</t>
+  </si>
+  <si>
+    <t>EMP_ID</t>
+  </si>
+  <si>
+    <t>EMP_FULL_NAME</t>
+  </si>
+  <si>
+    <t>THR_STATUS_PAJAK</t>
+  </si>
+  <si>
+    <t>THR_MASA_KERJA</t>
+  </si>
+  <si>
+    <t>THR_GAJI_POKOK</t>
+  </si>
+  <si>
+    <t>THR_TUNJANGAN_MASA_KERJA</t>
+  </si>
+  <si>
+    <t>THR_TUNJANGAN_GRADING</t>
+  </si>
+  <si>
+    <t>THR_TUNJANGAN_JABATAN</t>
+  </si>
+  <si>
+    <t>THR_TUNJANGAN_TIDAK_TETAP</t>
+  </si>
+  <si>
+    <t>THR_TOTAL_UPAH</t>
+  </si>
+  <si>
+    <t>THR_PPH</t>
+  </si>
+  <si>
+    <t>THR_COMPANY</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
+    <t>EMP_DEPARTEMEN</t>
+  </si>
+  <si>
+    <t>EMP_BAGIAN</t>
+  </si>
+  <si>
+    <t>EMP_JABATAN</t>
+  </si>
+  <si>
+    <t>CUTTING-1</t>
+  </si>
+  <si>
+    <t>A TIM</t>
+  </si>
+  <si>
+    <t>OPERATOR</t>
+  </si>
+  <si>
+    <t>EMBROIDERY</t>
+  </si>
+  <si>
+    <t>D TIM</t>
+  </si>
+  <si>
+    <t>SUPERVISOR</t>
+  </si>
+  <si>
+    <t>EMP_TANGGAL_MASUK</t>
+  </si>
+  <si>
+    <t>EMP_TANGGAL_KELUAR</t>
+  </si>
+  <si>
+    <t>2003-07-11</t>
+  </si>
+  <si>
+    <t>2003-07-16</t>
   </si>
 </sst>
 </file>
@@ -157,7 +196,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -174,6 +213,7 @@
     <xf numFmtId="41" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -489,71 +529,196 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C86984-557A-49A9-B90A-6FD29497B13B}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:T3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="8" width="25.7109375" customWidth="1"/>
-    <col min="9" max="19" width="15.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="35.140625" customWidth="1"/>
+    <col min="10" max="10" width="25.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="S1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="T1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>2025</v>
+      </c>
+      <c r="C2">
+        <v>300005</v>
+      </c>
+      <c r="D2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>260.8</v>
+      </c>
+      <c r="L2" s="6">
+        <v>2750140</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" s="6">
+        <v>105000</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="6">
+        <v>2855140</v>
+      </c>
+      <c r="R2" s="6">
+        <v>2855140</v>
+      </c>
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2" s="6">
+        <v>2855140</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3">
+        <v>300006</v>
+      </c>
+      <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
         <v>4</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>18</v>
+      <c r="K3">
+        <v>260.7</v>
+      </c>
+      <c r="L3" s="6">
+        <v>2750140</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="6">
+        <v>105000</v>
+      </c>
+      <c r="O3" s="6">
+        <v>50000</v>
+      </c>
+      <c r="P3" s="6">
+        <v>380000</v>
+      </c>
+      <c r="Q3" s="6">
+        <v>3285140</v>
+      </c>
+      <c r="R3" s="6">
+        <v>3285140</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3" s="6">
+        <v>3285140</v>
       </c>
     </row>
   </sheetData>

--- a/src/assets/excel/template-thr.xlsx
+++ b/src/assets/excel/template-thr.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\gbvh\src\assets\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\PROJECT\gbvh\gbvh\src\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2161CC-77A2-4F6B-98F9-9F0E83CF74F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18357B0A-9CCD-40A8-B8E7-2C95806D109B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D20C10B8-C708-4404-8118-FB0D135168E9}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{D20C10B8-C708-4404-8118-FB0D135168E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>THR_BRUTO</t>
   </si>
@@ -33,15 +33,6 @@
     <t>THR_BERSIH</t>
   </si>
   <si>
-    <t>HARTANTI</t>
-  </si>
-  <si>
-    <t>SRI WAHYUNINGSIH</t>
-  </si>
-  <si>
-    <t>TK/0</t>
-  </si>
-  <si>
     <t>THR_YEAR</t>
   </si>
   <si>
@@ -81,9 +72,6 @@
     <t>THR_COMPANY</t>
   </si>
   <si>
-    <t>PSG</t>
-  </si>
-  <si>
     <t>EMP_DEPARTEMEN</t>
   </si>
   <si>
@@ -93,34 +81,10 @@
     <t>EMP_JABATAN</t>
   </si>
   <si>
-    <t>CUTTING-1</t>
-  </si>
-  <si>
-    <t>A TIM</t>
-  </si>
-  <si>
-    <t>OPERATOR</t>
-  </si>
-  <si>
-    <t>EMBROIDERY</t>
-  </si>
-  <si>
-    <t>D TIM</t>
-  </si>
-  <si>
-    <t>SUPERVISOR</t>
-  </si>
-  <si>
     <t>EMP_TANGGAL_MASUK</t>
   </si>
   <si>
     <t>EMP_TANGGAL_KELUAR</t>
-  </si>
-  <si>
-    <t>2003-07-11</t>
-  </si>
-  <si>
-    <t>2003-07-16</t>
   </si>
 </sst>
 </file>
@@ -530,196 +494,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1C86984-557A-49A9-B90A-6FD29497B13B}">
   <dimension ref="A1:T3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="9" width="35.140625" customWidth="1"/>
-    <col min="10" max="10" width="25.7109375" customWidth="1"/>
-    <col min="11" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="15.7109375" customWidth="1"/>
+    <col min="2" max="3" width="15.6640625" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="35.109375" customWidth="1"/>
+    <col min="10" max="10" width="25.6640625" customWidth="1"/>
+    <col min="11" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="3" t="s">
+      <c r="M1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>15</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="T1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2">
-        <v>2025</v>
-      </c>
-      <c r="C2">
-        <v>300005</v>
-      </c>
-      <c r="D2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>4</v>
-      </c>
-      <c r="K2">
-        <v>260.8</v>
-      </c>
-      <c r="L2" s="6">
-        <v>2750140</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" s="6">
-        <v>105000</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>2855140</v>
-      </c>
-      <c r="R2" s="6">
-        <v>2855140</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2" s="6">
-        <v>2855140</v>
-      </c>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="L2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="T2" s="6"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>2025</v>
-      </c>
-      <c r="C3">
-        <v>300006</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>260.7</v>
-      </c>
-      <c r="L3" s="6">
-        <v>2750140</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" s="6">
-        <v>105000</v>
-      </c>
-      <c r="O3" s="6">
-        <v>50000</v>
-      </c>
-      <c r="P3" s="6">
-        <v>380000</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>3285140</v>
-      </c>
-      <c r="R3" s="6">
-        <v>3285140</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3" s="6">
-        <v>3285140</v>
-      </c>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="L3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="T3" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
